--- a/data/availability/projects/al-ahly-sabbour/youd.xlsx
+++ b/data/availability/projects/al-ahly-sabbour/youd.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delivery_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for youd-ras-el-hekma</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -737,7 +747,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +797,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +847,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +897,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -937,7 +947,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -987,7 +997,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1387,7 +1397,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1443,7 +1453,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1499,7 +1509,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1555,7 +1565,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1616,7 +1626,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1677,7 +1687,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1733,7 +1743,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1789,7 +1799,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
